--- a/港岛-坚尼地城-Kennedy 38/Kennedy 38_销控明细表.xlsx
+++ b/港岛-坚尼地城-Kennedy 38/Kennedy 38_销控明细表.xlsx
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="H38" s="5" t="n">
-        <v>8594000</v>
+        <v>8723000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>37528</v>
+        <v>38092</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -2990,14 +2990,14 @@
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>7734600</v>
+        <v>7850700</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>33776</v>
+        <v>34283</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>90 日付款計劃</t>
+          <t>90日付款計劃</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="H77" s="5" t="n">
-        <v>8385000</v>
+        <v>8511000</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>36616</v>
+        <v>37166</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5432,14 +5432,14 @@
         </is>
       </c>
       <c r="K77" s="5" t="n">
-        <v>7546500</v>
+        <v>7659900</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>32954</v>
+        <v>33449</v>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>90 日付款計劃</t>
+          <t>90日付款計劃</t>
         </is>
       </c>
       <c r="N77" s="3" t="inlineStr">
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -22620,8 +22620,8 @@
       <c r="I8" s="24" t="inlineStr">
         <is>
           <t>H | 229呎 (开放式)
-$859万
-$37,528/呎
+$872万
+$38,092/呎
 (暂停销售)</t>
         </is>
       </c>
@@ -22950,12 +22950,12 @@
 (25年-12月-04日)</t>
         </is>
       </c>
-      <c r="I11" s="24" t="inlineStr">
+      <c r="I11" s="23" t="inlineStr">
         <is>
           <t>H | 229呎 (开放式)
-$838万
-$36,616/呎
-(暂停销售)</t>
+$851万
+$37,166/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">

--- a/港岛-坚尼地城-Kennedy 38/Kennedy 38_销控明细表.xlsx
+++ b/港岛-坚尼地城-Kennedy 38/Kennedy 38_销控明细表.xlsx
@@ -5412,7 +5412,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -22189,12 +22189,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -22950,12 +22950,12 @@
 (25年-12月-04日)</t>
         </is>
       </c>
-      <c r="I11" s="23" t="inlineStr">
+      <c r="I11" s="25" t="inlineStr">
         <is>
           <t>H | 229呎 (开放式)
 $851万
 $37,166/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -23037,12 +23037,12 @@
 (21年-12月-17日)</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F12" s="25" t="inlineStr">
         <is>
           <t>E | 262呎 (开放式)
 $960万
 $36,660/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">

--- a/港岛-坚尼地城-Kennedy 38/Kennedy 38_销控明细表.xlsx
+++ b/港岛-坚尼地城-Kennedy 38/Kennedy 38_销控明细表.xlsx
@@ -5603,7 +5603,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -22931,7 +22931,7 @@
           <t>E | 262呎 (开放式)
 $869万
 $33,163/呎
-(26年-08月-25日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">

--- a/港岛-坚尼地城-Kennedy 38/Kennedy 38_销控明细表.xlsx
+++ b/港岛-坚尼地城-Kennedy 38/Kennedy 38_销控明细表.xlsx
@@ -6412,34 +6412,34 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
-        <v>9605000</v>
+        <v>8788500</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>36660</v>
+        <v>33544</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="5" t="n">
-        <v>8644500</v>
+        <v>8788500</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>32994</v>
+        <v>33544</v>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
-          <t>90 日付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N93" s="3" t="inlineStr">
@@ -22189,17 +22189,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -23037,12 +23037,12 @@
 (21年-12月-17日)</t>
         </is>
       </c>
-      <c r="F12" s="25" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 262呎 (开放式)
-$960万
-$36,660/呎
-(在售)</t>
+$879万
+$33,544/呎
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">

--- a/港岛-坚尼地城-Kennedy 38/Kennedy 38_销控明细表.xlsx
+++ b/港岛-坚尼地城-Kennedy 38/Kennedy 38_销控明细表.xlsx
@@ -6788,7 +6788,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>9408000</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>32219</v>
+        <v>32109</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>9408000</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>32219</v>
+        <v>32109</v>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
@@ -23206,9 +23206,9 @@
       </c>
       <c r="M13" s="20" t="inlineStr">
         <is>
-          <t>M | 292呎 (1房)
+          <t>M | 293呎 (1房)
 $941万
-$32,219/呎
+$32,109/呎
 (23年-05月-09日)</t>
         </is>
       </c>

--- a/港岛-坚尼地城-Kennedy 38/Kennedy 38_销控明细表.xlsx
+++ b/港岛-坚尼地城-Kennedy 38/Kennedy 38_销控明细表.xlsx
@@ -6417,7 +6417,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -23042,7 +23042,7 @@
           <t>E | 262呎 (开放式)
 $879万
 $33,544/呎
-(26年-09月-24日)</t>
+(26年-10月-15日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">

--- a/港岛-坚尼地城-Kennedy 38/Kennedy 38_销控明细表.xlsx
+++ b/港岛-坚尼地城-Kennedy 38/Kennedy 38_销控明细表.xlsx
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>35240000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>40045</v>
+        <v>40000</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>35240000</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>40045</v>
+        <v>40000</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>9622200</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>32074</v>
+        <v>31967</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>9622200</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>32074</v>
+        <v>31967</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>9630900</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>32870</v>
+        <v>32983</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>9630900</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>32870</v>
+        <v>32983</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>8703900</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>29208</v>
+        <v>29110</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>8703900</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>29208</v>
+        <v>29110</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>7416000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>32526</v>
+        <v>32384</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>7416000</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>32526</v>
+        <v>32384</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>8113500</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>30617</v>
+        <v>30733</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>8113500</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>30617</v>
+        <v>30733</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>9583200</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>32707</v>
+        <v>32819</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>9583200</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>32707</v>
+        <v>32819</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>7403400</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>32471</v>
+        <v>32329</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>7403400</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>32471</v>
+        <v>32329</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>8063000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>30426</v>
+        <v>30542</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>8063000</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>30426</v>
+        <v>30542</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>9319500</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>31065</v>
+        <v>30962</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>9319500</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>31065</v>
+        <v>30962</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>9535500</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>32544</v>
+        <v>32656</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>9535500</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>32544</v>
+        <v>32656</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         <v>8809000</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>29560</v>
+        <v>29462</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>8809000</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>29560</v>
+        <v>29462</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>8033400</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>30315</v>
+        <v>30430</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>8033400</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>30315</v>
+        <v>30430</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>10472300</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>31448</v>
+        <v>31543</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>10472300</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>31448</v>
+        <v>31543</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>9213300</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>32214</v>
+        <v>32102</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>9213300</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>32214</v>
+        <v>32102</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>9479600</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>31599</v>
+        <v>31494</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>9479600</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>31599</v>
+        <v>31494</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>9487800</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>32382</v>
+        <v>32492</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>9487800</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>32382</v>
+        <v>32492</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>8765700</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>29415</v>
+        <v>29317</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>8765700</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>29415</v>
+        <v>29317</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>7329600</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>32147</v>
+        <v>32007</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>7329600</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>32147</v>
+        <v>32007</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>7992900</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>30162</v>
+        <v>30276</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>7992900</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>30162</v>
+        <v>30276</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>9322000</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>32594</v>
+        <v>32481</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>9322000</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>32594</v>
+        <v>32481</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>9487800</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>32382</v>
+        <v>32492</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>9487800</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>32382</v>
+        <v>32492</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>8765700</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>29415</v>
+        <v>29317</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>8765700</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>29415</v>
+        <v>29317</v>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>7696800</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>33758</v>
+        <v>33610</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         <v>7696800</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>33758</v>
+        <v>33610</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>9384900</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>31283</v>
+        <v>31179</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>9384900</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>31283</v>
+        <v>31179</v>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>9393300</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>32059</v>
+        <v>32169</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5187,7 +5187,7 @@
         <v>9393300</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>32059</v>
+        <v>32169</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
         <v>7908300</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>29843</v>
+        <v>29956</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>7908300</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>29843</v>
+        <v>29956</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>10113300</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>30370</v>
+        <v>30462</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>10113300</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>30370</v>
+        <v>30462</v>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>9071100</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>31717</v>
+        <v>31607</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>9071100</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>31717</v>
+        <v>31607</v>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>9338900</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>31130</v>
+        <v>31026</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>9338900</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>31130</v>
+        <v>31026</v>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>9346500</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>31899</v>
+        <v>32009</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>9346500</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>31899</v>
+        <v>32009</v>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>8298000</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>27846</v>
+        <v>27753</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>8298000</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>27846</v>
+        <v>27753</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>7259400</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>31839</v>
+        <v>31700</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>7259400</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>31839</v>
+        <v>31700</v>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         <v>8043500</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>30353</v>
+        <v>30468</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>8043500</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>30353</v>
+        <v>30468</v>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>9027000</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>31563</v>
+        <v>31453</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>9027000</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>31563</v>
+        <v>31453</v>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>9408000</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>32109</v>
+        <v>32219</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>9408000</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>32109</v>
+        <v>32219</v>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>8257500</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>27710</v>
+        <v>27617</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>8257500</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>27710</v>
+        <v>27617</v>
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         </is>
       </c>
       <c r="E103" s="4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>7105400</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>31164</v>
+        <v>31028</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>7105400</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>31164</v>
+        <v>31028</v>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         </is>
       </c>
       <c r="E105" s="4" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>7964400</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>30054</v>
+        <v>30168</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>7964400</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>30054</v>
+        <v>30168</v>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
@@ -7618,7 +7618,7 @@
         <v>9157500</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>31254</v>
+        <v>31361</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
@@ -7629,7 +7629,7 @@
         <v>9157500</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>31254</v>
+        <v>31361</v>
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>8398600</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>28183</v>
+        <v>28089</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         <v>8398600</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>28183</v>
+        <v>28089</v>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>6873300</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>30146</v>
+        <v>30014</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>6873300</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>30146</v>
+        <v>30014</v>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         </is>
       </c>
       <c r="E118" s="4" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>7924800</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>29905</v>
+        <v>30018</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>7924800</v>
       </c>
       <c r="L118" s="5" t="n">
-        <v>29905</v>
+        <v>30018</v>
       </c>
       <c r="M118" s="3" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         </is>
       </c>
       <c r="E124" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>9069300</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>30231</v>
+        <v>30131</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
         <v>9069300</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>30231</v>
+        <v>30131</v>
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         </is>
       </c>
       <c r="E125" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>8881200</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>30311</v>
+        <v>30415</v>
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>8881200</v>
       </c>
       <c r="L125" s="5" t="n">
-        <v>30311</v>
+        <v>30415</v>
       </c>
       <c r="M125" s="3" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         </is>
       </c>
       <c r="E129" s="4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>6839100</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>29996</v>
+        <v>29865</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>6839100</v>
       </c>
       <c r="L129" s="5" t="n">
-        <v>29996</v>
+        <v>29865</v>
       </c>
       <c r="M129" s="3" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="E138" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>8703900</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>29706</v>
+        <v>29808</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>8703900</v>
       </c>
       <c r="L138" s="5" t="n">
-        <v>29706</v>
+        <v>29808</v>
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         </is>
       </c>
       <c r="E140" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>8314900</v>
       </c>
       <c r="I140" s="5" t="n">
-        <v>27902</v>
+        <v>27809</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>8314900</v>
       </c>
       <c r="L140" s="5" t="n">
-        <v>27902</v>
+        <v>27809</v>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="E142" s="4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>6804900</v>
       </c>
       <c r="I142" s="5" t="n">
-        <v>29846</v>
+        <v>29716</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         <v>6804900</v>
       </c>
       <c r="L142" s="5" t="n">
-        <v>29846</v>
+        <v>29716</v>
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         </is>
       </c>
       <c r="E144" s="4" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>7846600</v>
       </c>
       <c r="I144" s="5" t="n">
-        <v>29610</v>
+        <v>29722</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         <v>7846600</v>
       </c>
       <c r="L144" s="5" t="n">
-        <v>29610</v>
+        <v>29722</v>
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>8660700</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>29559</v>
+        <v>29660</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>8660700</v>
       </c>
       <c r="L151" s="5" t="n">
-        <v>29559</v>
+        <v>29660</v>
       </c>
       <c r="M151" s="3" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         </is>
       </c>
       <c r="E153" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v>8088300</v>
       </c>
       <c r="I153" s="5" t="n">
-        <v>27142</v>
+        <v>27051</v>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         <v>8088300</v>
       </c>
       <c r="L153" s="5" t="n">
-        <v>27142</v>
+        <v>27051</v>
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>6771600</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>29700</v>
+        <v>29570</v>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>6771600</v>
       </c>
       <c r="L155" s="5" t="n">
-        <v>29700</v>
+        <v>29570</v>
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         </is>
       </c>
       <c r="E157" s="4" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>7637400</v>
       </c>
       <c r="I157" s="5" t="n">
-        <v>28820</v>
+        <v>28930</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>7637400</v>
       </c>
       <c r="L157" s="5" t="n">
-        <v>28820</v>
+        <v>28930</v>
       </c>
       <c r="M157" s="3" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         </is>
       </c>
       <c r="E163" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>8848500</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>29495</v>
+        <v>29397</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>8848500</v>
       </c>
       <c r="L163" s="5" t="n">
-        <v>29495</v>
+        <v>29397</v>
       </c>
       <c r="M163" s="3" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         </is>
       </c>
       <c r="E164" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>8617500</v>
       </c>
       <c r="I164" s="5" t="n">
-        <v>29411</v>
+        <v>29512</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>8617500</v>
       </c>
       <c r="L164" s="5" t="n">
-        <v>29411</v>
+        <v>29512</v>
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         </is>
       </c>
       <c r="E168" s="4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>6737400</v>
       </c>
       <c r="I168" s="5" t="n">
-        <v>29550</v>
+        <v>29421</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>6737400</v>
       </c>
       <c r="L168" s="5" t="n">
-        <v>29550</v>
+        <v>29421</v>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         </is>
       </c>
       <c r="E177" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>8617500</v>
       </c>
       <c r="I177" s="5" t="n">
-        <v>29411</v>
+        <v>29512</v>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>8617500</v>
       </c>
       <c r="L177" s="5" t="n">
-        <v>29411</v>
+        <v>29512</v>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         </is>
       </c>
       <c r="E179" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>8227500</v>
       </c>
       <c r="I179" s="5" t="n">
-        <v>27609</v>
+        <v>27517</v>
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>8227500</v>
       </c>
       <c r="L179" s="5" t="n">
-        <v>27609</v>
+        <v>27517</v>
       </c>
       <c r="M179" s="3" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         </is>
       </c>
       <c r="E181" s="4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>6939900</v>
       </c>
       <c r="I181" s="5" t="n">
-        <v>30438</v>
+        <v>30305</v>
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>6939900</v>
       </c>
       <c r="L181" s="5" t="n">
-        <v>30438</v>
+        <v>30305</v>
       </c>
       <c r="M181" s="3" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         </is>
       </c>
       <c r="E190" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>8237700</v>
       </c>
       <c r="I190" s="5" t="n">
-        <v>28115</v>
+        <v>28211</v>
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>8237700</v>
       </c>
       <c r="L190" s="5" t="n">
-        <v>28115</v>
+        <v>28211</v>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         </is>
       </c>
       <c r="E194" s="4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>6637500</v>
       </c>
       <c r="I194" s="5" t="n">
-        <v>29112</v>
+        <v>28985</v>
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
@@ -12761,7 +12761,7 @@
         <v>6637500</v>
       </c>
       <c r="L194" s="5" t="n">
-        <v>29112</v>
+        <v>28985</v>
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         </is>
       </c>
       <c r="E200" s="4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>8443700</v>
       </c>
       <c r="I200" s="5" t="n">
-        <v>29523</v>
+        <v>29421</v>
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>8443700</v>
       </c>
       <c r="L200" s="5" t="n">
-        <v>29523</v>
+        <v>29421</v>
       </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         </is>
       </c>
       <c r="E202" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>8504400</v>
       </c>
       <c r="I202" s="5" t="n">
-        <v>28348</v>
+        <v>28254</v>
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>8504400</v>
       </c>
       <c r="L202" s="5" t="n">
-        <v>28348</v>
+        <v>28254</v>
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         </is>
       </c>
       <c r="E203" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>8350200</v>
       </c>
       <c r="I203" s="5" t="n">
-        <v>28499</v>
+        <v>28597</v>
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>8350200</v>
       </c>
       <c r="L203" s="5" t="n">
-        <v>28499</v>
+        <v>28597</v>
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         </is>
       </c>
       <c r="E207" s="4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>6464600</v>
       </c>
       <c r="I207" s="5" t="n">
-        <v>28354</v>
+        <v>28230</v>
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>6464600</v>
       </c>
       <c r="L207" s="5" t="n">
-        <v>28354</v>
+        <v>28230</v>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
@@ -13672,7 +13672,7 @@
         </is>
       </c>
       <c r="E209" s="4" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>7302600</v>
       </c>
       <c r="I209" s="5" t="n">
-        <v>27557</v>
+        <v>27661</v>
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>7302600</v>
       </c>
       <c r="L209" s="5" t="n">
-        <v>27557</v>
+        <v>27661</v>
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         </is>
       </c>
       <c r="E216" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>8189100</v>
       </c>
       <c r="I216" s="5" t="n">
-        <v>27949</v>
+        <v>28045</v>
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>8189100</v>
       </c>
       <c r="L216" s="5" t="n">
-        <v>27949</v>
+        <v>28045</v>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
@@ -14238,7 +14238,7 @@
         </is>
       </c>
       <c r="E218" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>8023300</v>
       </c>
       <c r="I218" s="5" t="n">
-        <v>26924</v>
+        <v>26834</v>
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         <v>8023300</v>
       </c>
       <c r="L218" s="5" t="n">
-        <v>26924</v>
+        <v>26834</v>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         </is>
       </c>
       <c r="E220" s="4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>6442200</v>
       </c>
       <c r="I220" s="5" t="n">
-        <v>28255</v>
+        <v>28132</v>
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>6442200</v>
       </c>
       <c r="L220" s="5" t="n">
-        <v>28255</v>
+        <v>28132</v>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         </is>
       </c>
       <c r="E222" s="4" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>7428000</v>
       </c>
       <c r="I222" s="5" t="n">
-        <v>28030</v>
+        <v>28136</v>
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>7428000</v>
       </c>
       <c r="L222" s="5" t="n">
-        <v>28030</v>
+        <v>28136</v>
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         </is>
       </c>
       <c r="E229" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
         <v>8186400</v>
       </c>
       <c r="I229" s="5" t="n">
-        <v>27940</v>
+        <v>28036</v>
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>8186400</v>
       </c>
       <c r="L229" s="5" t="n">
-        <v>27940</v>
+        <v>28036</v>
       </c>
       <c r="M229" s="3" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         </is>
       </c>
       <c r="E231" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         <v>7983700</v>
       </c>
       <c r="I231" s="5" t="n">
-        <v>26791</v>
+        <v>26701</v>
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>7983700</v>
       </c>
       <c r="L231" s="5" t="n">
-        <v>26791</v>
+        <v>26701</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         </is>
       </c>
       <c r="E233" s="4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>6399800</v>
       </c>
       <c r="I233" s="5" t="n">
-        <v>28069</v>
+        <v>27947</v>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
@@ -15203,7 +15203,7 @@
         <v>6399800</v>
       </c>
       <c r="L233" s="5" t="n">
-        <v>28069</v>
+        <v>27947</v>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         </is>
       </c>
       <c r="E235" s="4" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         <v>7390300</v>
       </c>
       <c r="I235" s="5" t="n">
-        <v>27888</v>
+        <v>27994</v>
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>7390300</v>
       </c>
       <c r="L235" s="5" t="n">
-        <v>27888</v>
+        <v>27994</v>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         </is>
       </c>
       <c r="E237" s="4" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>9509100</v>
       </c>
       <c r="I237" s="5" t="n">
-        <v>28556</v>
+        <v>28642</v>
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>9509100</v>
       </c>
       <c r="L237" s="5" t="n">
-        <v>28556</v>
+        <v>28642</v>
       </c>
       <c r="M237" s="3" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         </is>
       </c>
       <c r="E239" s="4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>8317700</v>
       </c>
       <c r="I239" s="5" t="n">
-        <v>29083</v>
+        <v>28982</v>
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>8317700</v>
       </c>
       <c r="L239" s="5" t="n">
-        <v>29083</v>
+        <v>28982</v>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         </is>
       </c>
       <c r="E241" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
@@ -15696,7 +15696,7 @@
         <v>8377500</v>
       </c>
       <c r="I241" s="5" t="n">
-        <v>27925</v>
+        <v>27832</v>
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>8377500</v>
       </c>
       <c r="L241" s="5" t="n">
-        <v>27925</v>
+        <v>27832</v>
       </c>
       <c r="M241" s="3" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         </is>
       </c>
       <c r="E244" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>7943200</v>
       </c>
       <c r="I244" s="5" t="n">
-        <v>26655</v>
+        <v>26566</v>
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>7943200</v>
       </c>
       <c r="L244" s="5" t="n">
-        <v>26655</v>
+        <v>26566</v>
       </c>
       <c r="M244" s="3" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         </is>
       </c>
       <c r="E246" s="4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>6520000</v>
       </c>
       <c r="I246" s="5" t="n">
-        <v>28596</v>
+        <v>28472</v>
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>6520000</v>
       </c>
       <c r="L246" s="5" t="n">
-        <v>28596</v>
+        <v>28472</v>
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         </is>
       </c>
       <c r="E248" s="4" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>7193700</v>
       </c>
       <c r="I248" s="5" t="n">
-        <v>27146</v>
+        <v>27249</v>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>7193700</v>
       </c>
       <c r="L248" s="5" t="n">
-        <v>27146</v>
+        <v>27249</v>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         </is>
       </c>
       <c r="E250" s="4" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>9156600</v>
       </c>
       <c r="I250" s="5" t="n">
-        <v>27497</v>
+        <v>27580</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>9156600</v>
       </c>
       <c r="L250" s="5" t="n">
-        <v>27497</v>
+        <v>27580</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         </is>
       </c>
       <c r="E254" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>8253300</v>
       </c>
       <c r="I254" s="5" t="n">
-        <v>27511</v>
+        <v>27420</v>
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>8253300</v>
       </c>
       <c r="L254" s="5" t="n">
-        <v>27511</v>
+        <v>27420</v>
       </c>
       <c r="M254" s="3" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
         </is>
       </c>
       <c r="E255" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>8035200</v>
       </c>
       <c r="I255" s="5" t="n">
-        <v>27424</v>
+        <v>27518</v>
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>8035200</v>
       </c>
       <c r="L255" s="5" t="n">
-        <v>27424</v>
+        <v>27518</v>
       </c>
       <c r="M255" s="3" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         </is>
       </c>
       <c r="E257" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>7903700</v>
       </c>
       <c r="I257" s="5" t="n">
-        <v>26522</v>
+        <v>26434</v>
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>7903700</v>
       </c>
       <c r="L257" s="5" t="n">
-        <v>26522</v>
+        <v>26434</v>
       </c>
       <c r="M257" s="3" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         </is>
       </c>
       <c r="E263" s="4" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F263" s="3" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>9267100</v>
       </c>
       <c r="I263" s="5" t="n">
-        <v>27829</v>
+        <v>27913</v>
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         <v>9267100</v>
       </c>
       <c r="L263" s="5" t="n">
-        <v>27829</v>
+        <v>27913</v>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         </is>
       </c>
       <c r="E265" s="4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>8153900</v>
       </c>
       <c r="I265" s="5" t="n">
-        <v>28510</v>
+        <v>28411</v>
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
@@ -17203,7 +17203,7 @@
         <v>8153900</v>
       </c>
       <c r="L265" s="5" t="n">
-        <v>28510</v>
+        <v>28411</v>
       </c>
       <c r="M265" s="3" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         </is>
       </c>
       <c r="E268" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>8035200</v>
       </c>
       <c r="I268" s="5" t="n">
-        <v>27424</v>
+        <v>27518</v>
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>8035200</v>
       </c>
       <c r="L268" s="5" t="n">
-        <v>27424</v>
+        <v>27518</v>
       </c>
       <c r="M268" s="3" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         </is>
       </c>
       <c r="E270" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>7903700</v>
       </c>
       <c r="I270" s="5" t="n">
-        <v>26522</v>
+        <v>26434</v>
       </c>
       <c r="J270" s="3" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>7903700</v>
       </c>
       <c r="L270" s="5" t="n">
-        <v>26522</v>
+        <v>26434</v>
       </c>
       <c r="M270" s="3" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         </is>
       </c>
       <c r="E272" s="4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>6486900</v>
       </c>
       <c r="I272" s="5" t="n">
-        <v>28451</v>
+        <v>28327</v>
       </c>
       <c r="J272" s="3" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>6486900</v>
       </c>
       <c r="L272" s="5" t="n">
-        <v>28451</v>
+        <v>28327</v>
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         </is>
       </c>
       <c r="E278" s="4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>8153900</v>
       </c>
       <c r="I278" s="5" t="n">
-        <v>28510</v>
+        <v>28411</v>
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>8153900</v>
       </c>
       <c r="L278" s="5" t="n">
-        <v>28510</v>
+        <v>28411</v>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         </is>
       </c>
       <c r="E281" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>7986600</v>
       </c>
       <c r="I281" s="5" t="n">
-        <v>27258</v>
+        <v>27351</v>
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>7986600</v>
       </c>
       <c r="L281" s="5" t="n">
-        <v>27258</v>
+        <v>27351</v>
       </c>
       <c r="M281" s="3" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         </is>
       </c>
       <c r="E283" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         <v>7824600</v>
       </c>
       <c r="I283" s="5" t="n">
-        <v>26257</v>
+        <v>26169</v>
       </c>
       <c r="J283" s="3" t="inlineStr">
         <is>
@@ -18335,7 +18335,7 @@
         <v>7824600</v>
       </c>
       <c r="L283" s="5" t="n">
-        <v>26257</v>
+        <v>26169</v>
       </c>
       <c r="M283" s="3" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         </is>
       </c>
       <c r="E287" s="4" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>7244000</v>
       </c>
       <c r="I287" s="5" t="n">
-        <v>27336</v>
+        <v>27439</v>
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>7244000</v>
       </c>
       <c r="L287" s="5" t="n">
-        <v>27336</v>
+        <v>27439</v>
       </c>
       <c r="M287" s="3" t="inlineStr">
         <is>
@@ -18680,7 +18680,7 @@
         </is>
       </c>
       <c r="E289" s="4" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>9075600</v>
       </c>
       <c r="I289" s="5" t="n">
-        <v>27254</v>
+        <v>27336</v>
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>9075600</v>
       </c>
       <c r="L289" s="5" t="n">
-        <v>27254</v>
+        <v>27336</v>
       </c>
       <c r="M289" s="3" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         </is>
       </c>
       <c r="E291" s="4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>8073000</v>
       </c>
       <c r="I291" s="5" t="n">
-        <v>28227</v>
+        <v>28129</v>
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>8073000</v>
       </c>
       <c r="L291" s="5" t="n">
-        <v>28227</v>
+        <v>28129</v>
       </c>
       <c r="M291" s="3" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         </is>
       </c>
       <c r="E293" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
         <v>8130000</v>
       </c>
       <c r="I293" s="5" t="n">
-        <v>27100</v>
+        <v>27010</v>
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>8130000</v>
       </c>
       <c r="L293" s="5" t="n">
-        <v>27100</v>
+        <v>27010</v>
       </c>
       <c r="M293" s="3" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         </is>
       </c>
       <c r="E294" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>8095900</v>
       </c>
       <c r="I294" s="5" t="n">
-        <v>27631</v>
+        <v>27726</v>
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
@@ -19025,7 +19025,7 @@
         <v>8095900</v>
       </c>
       <c r="L294" s="5" t="n">
-        <v>27631</v>
+        <v>27726</v>
       </c>
       <c r="M294" s="3" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         </is>
       </c>
       <c r="E304" s="4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F304" s="3" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>8041700</v>
       </c>
       <c r="I304" s="5" t="n">
-        <v>28118</v>
+        <v>28020</v>
       </c>
       <c r="J304" s="3" t="inlineStr">
         <is>
@@ -19645,7 +19645,7 @@
         <v>8041700</v>
       </c>
       <c r="L304" s="5" t="n">
-        <v>28118</v>
+        <v>28020</v>
       </c>
       <c r="M304" s="3" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         </is>
       </c>
       <c r="E306" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F306" s="3" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>8089500</v>
       </c>
       <c r="I306" s="5" t="n">
-        <v>26965</v>
+        <v>26875</v>
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>8089500</v>
       </c>
       <c r="L306" s="5" t="n">
-        <v>26965</v>
+        <v>26875</v>
       </c>
       <c r="M306" s="3" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         </is>
       </c>
       <c r="E307" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F307" s="3" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         <v>7938900</v>
       </c>
       <c r="I307" s="5" t="n">
-        <v>27095</v>
+        <v>27188</v>
       </c>
       <c r="J307" s="3" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>7938900</v>
       </c>
       <c r="L307" s="5" t="n">
-        <v>27095</v>
+        <v>27188</v>
       </c>
       <c r="M307" s="3" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="E311" s="4" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F311" s="3" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         <v>6346100</v>
       </c>
       <c r="I311" s="5" t="n">
-        <v>27834</v>
+        <v>27712</v>
       </c>
       <c r="J311" s="3" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         <v>6346100</v>
       </c>
       <c r="L311" s="5" t="n">
-        <v>27834</v>
+        <v>27712</v>
       </c>
       <c r="M311" s="3" t="inlineStr">
         <is>
@@ -20184,7 +20184,7 @@
         </is>
       </c>
       <c r="E313" s="4" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F313" s="3" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>7008300</v>
       </c>
       <c r="I313" s="5" t="n">
-        <v>26446</v>
+        <v>26547</v>
       </c>
       <c r="J313" s="3" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>7008300</v>
       </c>
       <c r="L313" s="5" t="n">
-        <v>26446</v>
+        <v>26547</v>
       </c>
       <c r="M313" s="3" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         </is>
       </c>
       <c r="E315" s="4" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F315" s="3" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>8984700</v>
       </c>
       <c r="I315" s="5" t="n">
-        <v>26981</v>
+        <v>27062</v>
       </c>
       <c r="J315" s="3" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>8984700</v>
       </c>
       <c r="L315" s="5" t="n">
-        <v>26981</v>
+        <v>27062</v>
       </c>
       <c r="M315" s="3" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         </is>
       </c>
       <c r="E319" s="4" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F319" s="3" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>8049000</v>
       </c>
       <c r="I319" s="5" t="n">
-        <v>26830</v>
+        <v>26741</v>
       </c>
       <c r="J319" s="3" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>8049000</v>
       </c>
       <c r="L319" s="5" t="n">
-        <v>26830</v>
+        <v>26741</v>
       </c>
       <c r="M319" s="3" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         </is>
       </c>
       <c r="E320" s="4" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F320" s="3" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>7915500</v>
       </c>
       <c r="I320" s="5" t="n">
-        <v>27015</v>
+        <v>27108</v>
       </c>
       <c r="J320" s="3" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         <v>7915500</v>
       </c>
       <c r="L320" s="5" t="n">
-        <v>27015</v>
+        <v>27108</v>
       </c>
       <c r="M320" s="3" t="inlineStr">
         <is>
@@ -20742,7 +20742,7 @@
         </is>
       </c>
       <c r="E322" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F322" s="3" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>7700400</v>
       </c>
       <c r="I322" s="5" t="n">
-        <v>25840</v>
+        <v>25754</v>
       </c>
       <c r="J322" s="3" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
         <v>7700400</v>
       </c>
       <c r="L322" s="5" t="n">
-        <v>25840</v>
+        <v>25754</v>
       </c>
       <c r="M322" s="3" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         </is>
       </c>
       <c r="E326" s="4" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F326" s="3" t="inlineStr">
         <is>
@@ -21006,7 +21006,7 @@
         <v>6973200</v>
       </c>
       <c r="I326" s="5" t="n">
-        <v>26314</v>
+        <v>26414</v>
       </c>
       <c r="J326" s="3" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>6973200</v>
       </c>
       <c r="L326" s="5" t="n">
-        <v>26314</v>
+        <v>26414</v>
       </c>
       <c r="M326" s="3" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         </is>
       </c>
       <c r="E328" s="4" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F328" s="3" t="inlineStr">
         <is>
@@ -21130,7 +21130,7 @@
         <v>8939600</v>
       </c>
       <c r="I328" s="5" t="n">
-        <v>26846</v>
+        <v>26927</v>
       </c>
       <c r="J328" s="3" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>8939600</v>
       </c>
       <c r="L328" s="5" t="n">
-        <v>26846</v>
+        <v>26927</v>
       </c>
       <c r="M328" s="3" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="E330" s="4" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F330" s="3" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>7784100</v>
       </c>
       <c r="I330" s="5" t="n">
-        <v>27217</v>
+        <v>27122</v>
       </c>
       <c r="J330" s="3" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>7784100</v>
       </c>
       <c r="L330" s="5" t="n">
-        <v>27217</v>
+        <v>27122</v>
       </c>
       <c r="M330" s="3" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         </is>
       </c>
       <c r="E338" s="4" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F338" s="3" t="inlineStr">
         <is>
@@ -21758,7 +21758,7 @@
         <v>8135100</v>
       </c>
       <c r="I338" s="5" t="n">
-        <v>30130</v>
+        <v>30019</v>
       </c>
       <c r="J338" s="3" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>8135100</v>
       </c>
       <c r="L338" s="5" t="n">
-        <v>30130</v>
+        <v>30019</v>
       </c>
       <c r="M338" s="3" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         </is>
       </c>
       <c r="E339" s="4" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F339" s="3" t="inlineStr">
         <is>
@@ -21820,7 +21820,7 @@
         <v>8043200</v>
       </c>
       <c r="I339" s="5" t="n">
-        <v>33236</v>
+        <v>33100</v>
       </c>
       <c r="J339" s="3" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>8043200</v>
       </c>
       <c r="L339" s="5" t="n">
-        <v>33236</v>
+        <v>33100</v>
       </c>
       <c r="M339" s="3" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         </is>
       </c>
       <c r="E342" s="4" t="n">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="F342" s="3" t="inlineStr">
         <is>
@@ -22317,9 +22317,9 @@
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>D | 880呎 (3房)
+          <t>D | 881呎 (3房)
 $3524万
-$40,045/呎
+$40,000/呎
 (24年-05月-09日)</t>
         </is>
       </c>
@@ -22381,9 +22381,9 @@
       </c>
       <c r="G6" s="20" t="inlineStr">
         <is>
-          <t>F | 265呎 (开放式)
+          <t>F | 264呎 (开放式)
 $811万
-$30,617/呎
+$30,733/呎
 (26年-03月-23日)</t>
         </is>
       </c>
@@ -22397,9 +22397,9 @@
       </c>
       <c r="I6" s="20" t="inlineStr">
         <is>
-          <t>H | 228呎 (开放式)
+          <t>H | 229呎 (开放式)
 $742万
-$32,526/呎
+$32,384/呎
 (26年-04月-01日)</t>
         </is>
       </c>
@@ -22413,9 +22413,9 @@
       </c>
       <c r="K6" s="20" t="inlineStr">
         <is>
-          <t>K | 298呎 (1房)
+          <t>K | 299呎 (1房)
 $870万
-$29,208/呎
+$29,110/呎
 (21年-12月-13日)</t>
         </is>
       </c>
@@ -22429,17 +22429,17 @@
       </c>
       <c r="M6" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $963万
-$32,870/呎
+$32,983/呎
 (25年-10月-23日)</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
         <is>
-          <t>N | 300呎 (1房)
+          <t>N | 301呎 (1房)
 $962万
-$32,074/呎
+$31,967/呎
 (21年-12月-17日)</t>
         </is>
       </c>
@@ -22492,9 +22492,9 @@
       </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
-          <t>F | 265呎 (开放式)
+          <t>F | 264呎 (开放式)
 $806万
-$30,426/呎
+$30,542/呎
 (25年-10月-28日)</t>
         </is>
       </c>
@@ -22508,9 +22508,9 @@
       </c>
       <c r="I7" s="20" t="inlineStr">
         <is>
-          <t>H | 228呎 (开放式)
+          <t>H | 229呎 (开放式)
 $740万
-$32,471/呎
+$32,329/呎
 (26年-03月-26日)</t>
         </is>
       </c>
@@ -22540,9 +22540,9 @@
       </c>
       <c r="M7" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $958万
-$32,707/呎
+$32,819/呎
 (25年-11月-26日)</t>
         </is>
       </c>
@@ -22571,9 +22571,9 @@
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>B | 286呎 (1房)
+          <t>B | 287呎 (1房)
 $921万
-$32,214/呎
+$32,102/呎
 (23年-04月-13日)</t>
         </is>
       </c>
@@ -22587,9 +22587,9 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>D | 333呎 (1房)
+          <t>D | 332呎 (1房)
 $1047万
-$31,448/呎
+$31,543/呎
 (22年-01月-28日)</t>
         </is>
       </c>
@@ -22603,9 +22603,9 @@
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
-          <t>F | 265呎 (开放式)
+          <t>F | 264呎 (开放式)
 $803万
-$30,315/呎
+$30,430/呎
 (26年-03月-25日)</t>
         </is>
       </c>
@@ -22635,9 +22635,9 @@
       </c>
       <c r="K8" s="20" t="inlineStr">
         <is>
-          <t>K | 298呎 (1房)
+          <t>K | 299呎 (1房)
 $881万
-$29,560/呎
+$29,462/呎
 (21年-12月-15日)</t>
         </is>
       </c>
@@ -22651,17 +22651,17 @@
       </c>
       <c r="M8" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $954万
-$32,544/呎
+$32,656/呎
 (24年-03月-28日)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr">
         <is>
-          <t>N | 300呎 (1房)
+          <t>N | 301呎 (1房)
 $932万
-$31,065/呎
+$30,962/呎
 (21年-12月-13日)</t>
         </is>
       </c>
@@ -22682,9 +22682,9 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>B | 286呎 (1房)
+          <t>B | 287呎 (1房)
 $932万
-$32,594/呎
+$32,481/呎
 (24年-06月-04日)</t>
         </is>
       </c>
@@ -22714,9 +22714,9 @@
       </c>
       <c r="G9" s="20" t="inlineStr">
         <is>
-          <t>F | 265呎 (开放式)
+          <t>F | 264呎 (开放式)
 $799万
-$30,162/呎
+$30,276/呎
 (26年-02月-27日)</t>
         </is>
       </c>
@@ -22730,9 +22730,9 @@
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
-          <t>H | 228呎 (开放式)
+          <t>H | 229呎 (开放式)
 $733万
-$32,147/呎
+$32,007/呎
 (26年-04月-14日)</t>
         </is>
       </c>
@@ -22746,9 +22746,9 @@
       </c>
       <c r="K9" s="20" t="inlineStr">
         <is>
-          <t>K | 298呎 (1房)
+          <t>K | 299呎 (1房)
 $877万
-$29,415/呎
+$29,317/呎
 (21年-12月-15日)</t>
         </is>
       </c>
@@ -22762,17 +22762,17 @@
       </c>
       <c r="M9" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $949万
-$32,382/呎
+$32,492/呎
 (24年-03月-25日)</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
         <is>
-          <t>N | 300呎 (1房)
+          <t>N | 301呎 (1房)
 $948万
-$31,599/呎
+$31,494/呎
 (21年-12月-17日)</t>
         </is>
       </c>
@@ -22841,9 +22841,9 @@
       </c>
       <c r="I10" s="20" t="inlineStr">
         <is>
-          <t>H | 228呎 (开放式)
+          <t>H | 229呎 (开放式)
 $770万
-$33,758/呎
+$33,610/呎
 (26年-06月-15日)</t>
         </is>
       </c>
@@ -22857,9 +22857,9 @@
       </c>
       <c r="K10" s="20" t="inlineStr">
         <is>
-          <t>K | 298呎 (1房)
+          <t>K | 299呎 (1房)
 $877万
-$29,415/呎
+$29,317/呎
 (21年-12月-15日)</t>
         </is>
       </c>
@@ -22873,9 +22873,9 @@
       </c>
       <c r="M10" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $949万
-$32,382/呎
+$32,492/呎
 (25年-07月-28日)</t>
         </is>
       </c>
@@ -22904,9 +22904,9 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>B | 286呎 (1房)
+          <t>B | 287呎 (1房)
 $907万
-$31,717/呎
+$31,607/呎
 (25年-11月-12日)</t>
         </is>
       </c>
@@ -22920,9 +22920,9 @@
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>D | 333呎 (1房)
+          <t>D | 332呎 (1房)
 $1011万
-$30,370/呎
+$30,462/呎
 (21年-12月-14日)</t>
         </is>
       </c>
@@ -22936,9 +22936,9 @@
       </c>
       <c r="G11" s="20" t="inlineStr">
         <is>
-          <t>F | 265呎 (开放式)
+          <t>F | 264呎 (开放式)
 $791万
-$29,843/呎
+$29,956/呎
 (26年-02月-06日)</t>
         </is>
       </c>
@@ -22984,17 +22984,17 @@
       </c>
       <c r="M11" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $939万
-$32,059/呎
+$32,169/呎
 (25年-07月-28日)</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
         <is>
-          <t>N | 300呎 (1房)
+          <t>N | 301呎 (1房)
 $938万
-$31,283/呎
+$31,179/呎
 (21年-12月-13日)</t>
         </is>
       </c>
@@ -23015,9 +23015,9 @@
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>B | 286呎 (1房)
+          <t>B | 287呎 (1房)
 $903万
-$31,563/呎
+$31,453/呎
 (25年-11月-20日)</t>
         </is>
       </c>
@@ -23047,9 +23047,9 @@
       </c>
       <c r="G12" s="20" t="inlineStr">
         <is>
-          <t>F | 265呎 (开放式)
+          <t>F | 264呎 (开放式)
 $804万
-$30,353/呎
+$30,468/呎
 (22年-03月-09日)</t>
         </is>
       </c>
@@ -23063,9 +23063,9 @@
       </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
-          <t>H | 228呎 (开放式)
+          <t>H | 229呎 (开放式)
 $726万
-$31,839/呎
+$31,700/呎
 (26年-04月-28日)</t>
         </is>
       </c>
@@ -23079,9 +23079,9 @@
       </c>
       <c r="K12" s="20" t="inlineStr">
         <is>
-          <t>K | 298呎 (1房)
+          <t>K | 299呎 (1房)
 $830万
-$27,846/呎
+$27,753/呎
 (21年-12月-13日)</t>
         </is>
       </c>
@@ -23095,17 +23095,17 @@
       </c>
       <c r="M12" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $935万
-$31,899/呎
+$32,009/呎
 (23年-12月-15日)</t>
         </is>
       </c>
       <c r="N12" s="20" t="inlineStr">
         <is>
-          <t>N | 300呎 (1房)
+          <t>N | 301呎 (1房)
 $934万
-$31,130/呎
+$31,026/呎
 (21年-12月-21日)</t>
         </is>
       </c>
@@ -23158,9 +23158,9 @@
       </c>
       <c r="G13" s="20" t="inlineStr">
         <is>
-          <t>F | 265呎 (开放式)
+          <t>F | 264呎 (开放式)
 $796万
-$30,054/呎
+$30,168/呎
 (21年-11月-20日)</t>
         </is>
       </c>
@@ -23174,9 +23174,9 @@
       </c>
       <c r="I13" s="20" t="inlineStr">
         <is>
-          <t>H | 228呎 (开放式)
+          <t>H | 229呎 (开放式)
 $711万
-$31,164/呎
+$31,028/呎
 (26年-04月-02日)</t>
         </is>
       </c>
@@ -23190,9 +23190,9 @@
       </c>
       <c r="K13" s="20" t="inlineStr">
         <is>
-          <t>K | 298呎 (1房)
+          <t>K | 299呎 (1房)
 $826万
-$27,710/呎
+$27,617/呎
 (21年-12月-13日)</t>
         </is>
       </c>
@@ -23206,9 +23206,9 @@
       </c>
       <c r="M13" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $941万
-$32,109/呎
+$32,219/呎
 (23年-05月-09日)</t>
         </is>
       </c>
@@ -23269,9 +23269,9 @@
       </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
-          <t>F | 265呎 (开放式)
+          <t>F | 264呎 (开放式)
 $792万
-$29,905/呎
+$30,018/呎
 (21年-12月-09日)</t>
         </is>
       </c>
@@ -23285,9 +23285,9 @@
       </c>
       <c r="I14" s="20" t="inlineStr">
         <is>
-          <t>H | 228呎 (开放式)
+          <t>H | 229呎 (开放式)
 $687万
-$30,146/呎
+$30,014/呎
 (26年-03月-20日)</t>
         </is>
       </c>
@@ -23301,9 +23301,9 @@
       </c>
       <c r="K14" s="20" t="inlineStr">
         <is>
-          <t>K | 298呎 (1房)
+          <t>K | 299呎 (1房)
 $840万
-$28,183/呎
+$28,089/呎
 (21年-12月-17日)</t>
         </is>
       </c>
@@ -23317,9 +23317,9 @@
       </c>
       <c r="M14" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $916万
-$31,254/呎
+$31,361/呎
 (25年-07月-25日)</t>
         </is>
       </c>
@@ -23396,9 +23396,9 @@
       </c>
       <c r="I15" s="20" t="inlineStr">
         <is>
-          <t>H | 228呎 (开放式)
+          <t>H | 229呎 (开放式)
 $684万
-$29,996/呎
+$29,865/呎
 (26年-03月-19日)</t>
         </is>
       </c>
@@ -23428,17 +23428,17 @@
       </c>
       <c r="M15" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $888万
-$30,311/呎
+$30,415/呎
 (24年-02月-29日)</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
         <is>
-          <t>N | 300呎 (1房)
+          <t>N | 301呎 (1房)
 $907万
-$30,231/呎
+$30,131/呎
 (21年-12月-17日)</t>
         </is>
       </c>
@@ -23491,9 +23491,9 @@
       </c>
       <c r="G16" s="20" t="inlineStr">
         <is>
-          <t>F | 265呎 (开放式)
+          <t>F | 264呎 (开放式)
 $785万
-$29,610/呎
+$29,722/呎
 (21年-12月-10日)</t>
         </is>
       </c>
@@ -23507,9 +23507,9 @@
       </c>
       <c r="I16" s="20" t="inlineStr">
         <is>
-          <t>H | 228呎 (开放式)
+          <t>H | 229呎 (开放式)
 $680万
-$29,846/呎
+$29,716/呎
 (26年-01月-13日)</t>
         </is>
       </c>
@@ -23523,9 +23523,9 @@
       </c>
       <c r="K16" s="20" t="inlineStr">
         <is>
-          <t>K | 298呎 (1房)
+          <t>K | 299呎 (1房)
 $831万
-$27,902/呎
+$27,809/呎
 (21年-12月-22日)</t>
         </is>
       </c>
@@ -23539,9 +23539,9 @@
       </c>
       <c r="M16" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $870万
-$29,706/呎
+$29,808/呎
 (25年-05月-14日)</t>
         </is>
       </c>
@@ -23602,9 +23602,9 @@
       </c>
       <c r="G17" s="20" t="inlineStr">
         <is>
-          <t>F | 265呎 (开放式)
+          <t>F | 264呎 (开放式)
 $764万
-$28,820/呎
+$28,930/呎
 (21年-12月-10日)</t>
         </is>
       </c>
@@ -23618,9 +23618,9 @@
       </c>
       <c r="I17" s="20" t="inlineStr">
         <is>
-          <t>H | 228呎 (开放式)
+          <t>H | 229呎 (开放式)
 $677万
-$29,700/呎
+$29,570/呎
 (25年-12月-31日)</t>
         </is>
       </c>
@@ -23634,9 +23634,9 @@
       </c>
       <c r="K17" s="20" t="inlineStr">
         <is>
-          <t>K | 298呎 (1房)
+          <t>K | 299呎 (1房)
 $809万
-$27,142/呎
+$27,051/呎
 (21年-11月-20日)</t>
         </is>
       </c>
@@ -23650,9 +23650,9 @@
       </c>
       <c r="M17" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $866万
-$29,559/呎
+$29,660/呎
 (25年-12月-15日)</t>
         </is>
       </c>
@@ -23729,9 +23729,9 @@
       </c>
       <c r="I18" s="20" t="inlineStr">
         <is>
-          <t>H | 228呎 (开放式)
+          <t>H | 229呎 (开放式)
 $674万
-$29,550/呎
+$29,421/呎
 (26年-02月-09日)</t>
         </is>
       </c>
@@ -23761,17 +23761,17 @@
       </c>
       <c r="M18" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $862万
-$29,411/呎
+$29,512/呎
 (25年-12月-04日)</t>
         </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
-          <t>N | 300呎 (1房)
+          <t>N | 301呎 (1房)
 $885万
-$29,495/呎
+$29,397/呎
 (21年-12月-14日)</t>
         </is>
       </c>
@@ -23840,9 +23840,9 @@
       </c>
       <c r="I19" s="20" t="inlineStr">
         <is>
-          <t>H | 228呎 (开放式)
+          <t>H | 229呎 (开放式)
 $694万
-$30,438/呎
+$30,305/呎
 (26年-04月-22日)</t>
         </is>
       </c>
@@ -23856,9 +23856,9 @@
       </c>
       <c r="K19" s="20" t="inlineStr">
         <is>
-          <t>K | 298呎 (1房)
+          <t>K | 299呎 (1房)
 $823万
-$27,609/呎
+$27,517/呎
 (21年-12月-14日)</t>
         </is>
       </c>
@@ -23872,9 +23872,9 @@
       </c>
       <c r="M19" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $862万
-$29,411/呎
+$29,512/呎
 (25年-11月-19日)</t>
         </is>
       </c>
@@ -23903,9 +23903,9 @@
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>B | 286呎 (1房)
+          <t>B | 287呎 (1房)
 $844万
-$29,523/呎
+$29,421/呎
 (21年-12月-22日)</t>
         </is>
       </c>
@@ -23951,9 +23951,9 @@
       </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
-          <t>H | 228呎 (开放式)
+          <t>H | 229呎 (开放式)
 $664万
-$29,112/呎
+$28,985/呎
 (26年-01月-15日)</t>
         </is>
       </c>
@@ -23983,9 +23983,9 @@
       </c>
       <c r="M20" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $824万
-$28,115/呎
+$28,211/呎
 (24年-06月-11日)</t>
         </is>
       </c>
@@ -24046,9 +24046,9 @@
       </c>
       <c r="G21" s="20" t="inlineStr">
         <is>
-          <t>F | 265呎 (开放式)
+          <t>F | 264呎 (开放式)
 $730万
-$27,557/呎
+$27,661/呎
 (25年-06月-17日)</t>
         </is>
       </c>
@@ -24062,9 +24062,9 @@
       </c>
       <c r="I21" s="20" t="inlineStr">
         <is>
-          <t>H | 228呎 (开放式)
+          <t>H | 229呎 (开放式)
 $646万
-$28,354/呎
+$28,230/呎
 (26年-01月-05日)</t>
         </is>
       </c>
@@ -24094,17 +24094,17 @@
       </c>
       <c r="M21" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $835万
-$28,499/呎
+$28,597/呎
 (24年-02月-19日)</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
         <is>
-          <t>N | 300呎 (1房)
+          <t>N | 301呎 (1房)
 $850万
-$28,348/呎
+$28,254/呎
 (21年-12月-10日)</t>
         </is>
       </c>
@@ -24157,9 +24157,9 @@
       </c>
       <c r="G22" s="20" t="inlineStr">
         <is>
-          <t>F | 265呎 (开放式)
+          <t>F | 264呎 (开放式)
 $743万
-$28,030/呎
+$28,136/呎
 (21年-12月-15日)</t>
         </is>
       </c>
@@ -24173,9 +24173,9 @@
       </c>
       <c r="I22" s="20" t="inlineStr">
         <is>
-          <t>H | 228呎 (开放式)
+          <t>H | 229呎 (开放式)
 $644万
-$28,255/呎
+$28,132/呎
 (25年-12月-29日)</t>
         </is>
       </c>
@@ -24189,9 +24189,9 @@
       </c>
       <c r="K22" s="20" t="inlineStr">
         <is>
-          <t>K | 298呎 (1房)
+          <t>K | 299呎 (1房)
 $802万
-$26,924/呎
+$26,834/呎
 (21年-12月-09日)</t>
         </is>
       </c>
@@ -24205,9 +24205,9 @@
       </c>
       <c r="M22" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $819万
-$27,949/呎
+$28,045/呎
 (23年-05月-30日)</t>
         </is>
       </c>
@@ -24236,9 +24236,9 @@
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>B | 286呎 (1房)
+          <t>B | 287呎 (1房)
 $832万
-$29,083/呎
+$28,982/呎
 (21年-12月-20日)</t>
         </is>
       </c>
@@ -24252,9 +24252,9 @@
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>D | 333呎 (1房)
+          <t>D | 332呎 (1房)
 $951万
-$28,556/呎
+$28,642/呎
 (21年-12月-17日)</t>
         </is>
       </c>
@@ -24268,9 +24268,9 @@
       </c>
       <c r="G23" s="20" t="inlineStr">
         <is>
-          <t>F | 265呎 (开放式)
+          <t>F | 264呎 (开放式)
 $739万
-$27,888/呎
+$27,994/呎
 (21年-12月-13日)</t>
         </is>
       </c>
@@ -24284,9 +24284,9 @@
       </c>
       <c r="I23" s="20" t="inlineStr">
         <is>
-          <t>H | 228呎 (开放式)
+          <t>H | 229呎 (开放式)
 $640万
-$28,069/呎
+$27,947/呎
 (25年-11月-26日)</t>
         </is>
       </c>
@@ -24300,9 +24300,9 @@
       </c>
       <c r="K23" s="20" t="inlineStr">
         <is>
-          <t>K | 298呎 (1房)
+          <t>K | 299呎 (1房)
 $798万
-$26,791/呎
+$26,701/呎
 (21年-12月-09日)</t>
         </is>
       </c>
@@ -24316,9 +24316,9 @@
       </c>
       <c r="M23" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $819万
-$27,940/呎
+$28,036/呎
 (25年-08月-06日)</t>
         </is>
       </c>
@@ -24363,9 +24363,9 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>D | 333呎 (1房)
+          <t>D | 332呎 (1房)
 $916万
-$27,497/呎
+$27,580/呎
 (21年-12月-10日)</t>
         </is>
       </c>
@@ -24379,9 +24379,9 @@
       </c>
       <c r="G24" s="20" t="inlineStr">
         <is>
-          <t>F | 265呎 (开放式)
+          <t>F | 264呎 (开放式)
 $719万
-$27,146/呎
+$27,249/呎
 (21年-11月-20日)</t>
         </is>
       </c>
@@ -24395,9 +24395,9 @@
       </c>
       <c r="I24" s="20" t="inlineStr">
         <is>
-          <t>H | 228呎 (开放式)
+          <t>H | 229呎 (开放式)
 $652万
-$28,596/呎
+$28,472/呎
 (22年-01月-12日)</t>
         </is>
       </c>
@@ -24411,9 +24411,9 @@
       </c>
       <c r="K24" s="20" t="inlineStr">
         <is>
-          <t>K | 298呎 (1房)
+          <t>K | 299呎 (1房)
 $794万
-$26,655/呎
+$26,566/呎
 (21年-12月-10日)</t>
         </is>
       </c>
@@ -24435,9 +24435,9 @@
       </c>
       <c r="N24" s="20" t="inlineStr">
         <is>
-          <t>N | 300呎 (1房)
+          <t>N | 301呎 (1房)
 $838万
-$27,925/呎
+$27,832/呎
 (21年-12月-20日)</t>
         </is>
       </c>
@@ -24458,9 +24458,9 @@
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>B | 286呎 (1房)
+          <t>B | 287呎 (1房)
 $815万
-$28,510/呎
+$28,411/呎
 (21年-12月-17日)</t>
         </is>
       </c>
@@ -24474,9 +24474,9 @@
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
-          <t>D | 333呎 (1房)
+          <t>D | 332呎 (1房)
 $927万
-$27,829/呎
+$27,913/呎
 (21年-12月-15日)</t>
         </is>
       </c>
@@ -24522,9 +24522,9 @@
       </c>
       <c r="K25" s="20" t="inlineStr">
         <is>
-          <t>K | 298呎 (1房)
+          <t>K | 299呎 (1房)
 $790万
-$26,522/呎
+$26,434/呎
 (21年-12月-08日)</t>
         </is>
       </c>
@@ -24538,17 +24538,17 @@
       </c>
       <c r="M25" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $804万
-$27,424/呎
+$27,518/呎
 (24年-07月-08日)</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
         <is>
-          <t>N | 300呎 (1房)
+          <t>N | 301呎 (1房)
 $825万
-$27,511/呎
+$27,420/呎
 (21年-12月-16日)</t>
         </is>
       </c>
@@ -24569,9 +24569,9 @@
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>B | 286呎 (1房)
+          <t>B | 287呎 (1房)
 $815万
-$28,510/呎
+$28,411/呎
 (21年-12月-17日)</t>
         </is>
       </c>
@@ -24617,9 +24617,9 @@
       </c>
       <c r="I26" s="20" t="inlineStr">
         <is>
-          <t>H | 228呎 (开放式)
+          <t>H | 229呎 (开放式)
 $649万
-$28,451/呎
+$28,327/呎
 (21年-12月-14日)</t>
         </is>
       </c>
@@ -24633,9 +24633,9 @@
       </c>
       <c r="K26" s="20" t="inlineStr">
         <is>
-          <t>K | 298呎 (1房)
+          <t>K | 299呎 (1房)
 $790万
-$26,522/呎
+$26,434/呎
 (21年-12月-08日)</t>
         </is>
       </c>
@@ -24649,9 +24649,9 @@
       </c>
       <c r="M26" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $804万
-$27,424/呎
+$27,518/呎
 (25年-09月-12日)</t>
         </is>
       </c>
@@ -24680,9 +24680,9 @@
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>B | 286呎 (1房)
+          <t>B | 287呎 (1房)
 $807万
-$28,227/呎
+$28,129/呎
 (21年-12月-17日)</t>
         </is>
       </c>
@@ -24696,9 +24696,9 @@
       </c>
       <c r="E27" s="20" t="inlineStr">
         <is>
-          <t>D | 333呎 (1房)
+          <t>D | 332呎 (1房)
 $908万
-$27,254/呎
+$27,336/呎
 (24年-12月-23日)</t>
         </is>
       </c>
@@ -24712,9 +24712,9 @@
       </c>
       <c r="G27" s="20" t="inlineStr">
         <is>
-          <t>F | 265呎 (开放式)
+          <t>F | 264呎 (开放式)
 $724万
-$27,336/呎
+$27,439/呎
 (21年-12月-17日)</t>
         </is>
       </c>
@@ -24744,9 +24744,9 @@
       </c>
       <c r="K27" s="20" t="inlineStr">
         <is>
-          <t>K | 298呎 (1房)
+          <t>K | 299呎 (1房)
 $782万
-$26,257/呎
+$26,169/呎
 (21年-12月-17日)</t>
         </is>
       </c>
@@ -24760,9 +24760,9 @@
       </c>
       <c r="M27" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $799万
-$27,258/呎
+$27,351/呎
 (24年-05月-09日)</t>
         </is>
       </c>
@@ -24791,9 +24791,9 @@
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>B | 286呎 (1房)
+          <t>B | 287呎 (1房)
 $804万
-$28,118/呎
+$28,020/呎
 (21年-12月-23日)</t>
         </is>
       </c>
@@ -24871,17 +24871,17 @@
       </c>
       <c r="M28" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $810万
-$27,631/呎
+$27,726/呎
 (24年-04月-23日)</t>
         </is>
       </c>
       <c r="N28" s="20" t="inlineStr">
         <is>
-          <t>N | 300呎 (1房)
+          <t>N | 301呎 (1房)
 $813万
-$27,100/呎
+$27,010/呎
 (21年-12月-14日)</t>
         </is>
       </c>
@@ -24918,9 +24918,9 @@
       </c>
       <c r="E29" s="20" t="inlineStr">
         <is>
-          <t>D | 333呎 (1房)
+          <t>D | 332呎 (1房)
 $898万
-$26,981/呎
+$27,062/呎
 (21年-12月-16日)</t>
         </is>
       </c>
@@ -24934,9 +24934,9 @@
       </c>
       <c r="G29" s="20" t="inlineStr">
         <is>
-          <t>F | 265呎 (开放式)
+          <t>F | 264呎 (开放式)
 $701万
-$26,446/呎
+$26,547/呎
 (25年-12月-12日)</t>
         </is>
       </c>
@@ -24950,9 +24950,9 @@
       </c>
       <c r="I29" s="20" t="inlineStr">
         <is>
-          <t>H | 228呎 (开放式)
+          <t>H | 229呎 (开放式)
 $635万
-$27,834/呎
+$27,712/呎
 (22年-09月-20日)</t>
         </is>
       </c>
@@ -24982,17 +24982,17 @@
       </c>
       <c r="M29" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $794万
-$27,095/呎
+$27,188/呎
 (25年-09月-05日)</t>
         </is>
       </c>
       <c r="N29" s="20" t="inlineStr">
         <is>
-          <t>N | 300呎 (1房)
+          <t>N | 301呎 (1房)
 $809万
-$26,965/呎
+$26,875/呎
 (21年-12月-14日)</t>
         </is>
       </c>
@@ -25013,9 +25013,9 @@
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>B | 286呎 (1房)
+          <t>B | 287呎 (1房)
 $778万
-$27,217/呎
+$27,122/呎
 (22年-01月-13日)</t>
         </is>
       </c>
@@ -25029,9 +25029,9 @@
       </c>
       <c r="E30" s="20" t="inlineStr">
         <is>
-          <t>D | 333呎 (1房)
+          <t>D | 332呎 (1房)
 $894万
-$26,846/呎
+$26,927/呎
 (21年-12月-13日)</t>
         </is>
       </c>
@@ -25045,9 +25045,9 @@
       </c>
       <c r="G30" s="20" t="inlineStr">
         <is>
-          <t>F | 265呎 (开放式)
+          <t>F | 264呎 (开放式)
 $697万
-$26,314/呎
+$26,414/呎
 (25年-12月-24日)</t>
         </is>
       </c>
@@ -25077,9 +25077,9 @@
       </c>
       <c r="K30" s="20" t="inlineStr">
         <is>
-          <t>K | 298呎 (1房)
+          <t>K | 299呎 (1房)
 $770万
-$25,840/呎
+$25,754/呎
 (21年-12月-22日)</t>
         </is>
       </c>
@@ -25093,17 +25093,17 @@
       </c>
       <c r="M30" s="20" t="inlineStr">
         <is>
-          <t>M | 293呎 (1房)
+          <t>M | 292呎 (1房)
 $792万
-$27,015/呎
+$27,108/呎
 (25年-12月-04日)</t>
         </is>
       </c>
       <c r="N30" s="20" t="inlineStr">
         <is>
-          <t>N | 300呎 (1房)
+          <t>N | 301呎 (1房)
 $805万
-$26,830/呎
+$26,741/呎
 (21年-12月-16日)</t>
         </is>
       </c>
@@ -25124,7 +25124,7 @@
       </c>
       <c r="C31" s="25" t="inlineStr">
         <is>
-          <t>B | 687呎 (4+房)
+          <t>B | 686呎 (4+房)
 招标单位
 -
 (在售)</t>
@@ -25148,17 +25148,17 @@
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>E | 242呎 (开放式)
+          <t>E | 243呎 (开放式)
 $804万
-$33,236/呎
+$33,100/呎
 (26年-07月-24日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
         <is>
-          <t>F | 270呎 (1房)
+          <t>F | 271呎 (1房)
 $814万
-$30,130/呎
+$30,019/呎
 (21年-12月-17日)</t>
         </is>
       </c>
